--- a/AAII_Financials/Yearly/EHLD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EHLD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>EHLD</t>
   </si>
@@ -1483,8 +1483,8 @@
       <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
+      <c r="F41" s="3">
+        <v>800</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1537,8 +1537,8 @@
       <c r="E43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3">
+        <v>2000</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -1564,8 +1564,8 @@
       <c r="E44" s="3">
         <v>300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
+      <c r="F44" s="3">
+        <v>300</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -1618,8 +1618,8 @@
       <c r="E46" s="3">
         <v>2300</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
+      <c r="F46" s="3">
+        <v>3100</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1672,8 +1672,8 @@
       <c r="E48" s="3">
         <v>6000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+      <c r="F48" s="3">
+        <v>6900</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1699,8 +1699,8 @@
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+      <c r="F49" s="3">
+        <v>0</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -1834,8 +1834,8 @@
       <c r="E54" s="3">
         <v>8200</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
+      <c r="F54" s="3">
+        <v>10000</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -1887,8 +1887,8 @@
       <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+      <c r="F57" s="3">
+        <v>500</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -1914,8 +1914,8 @@
       <c r="E58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="F58" s="3">
+        <v>700</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -1941,8 +1941,8 @@
       <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+      <c r="F59" s="3">
+        <v>400</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -1968,8 +1968,8 @@
       <c r="E60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
+      <c r="F60" s="3">
+        <v>1800</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -1996,7 +1996,7 @@
         <v>1200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2130,8 +2130,8 @@
       <c r="E66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
+      <c r="F66" s="3">
+        <v>3700</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2386,8 +2386,8 @@
       <c r="E76" s="3">
         <v>5700</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
+      <c r="F76" s="3">
+        <v>6300</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
